--- a/data/analysis_results/gpt-4.1_vs_Llama-2-7b-chat-hf/Mistral-7B-Instruct-v0.2/basic/total_votes_file.xlsx
+++ b/data/analysis_results/gpt-4.1_vs_Llama-2-7b-chat-hf/Mistral-7B-Instruct-v0.2/basic/total_votes_file.xlsx
@@ -37,10 +37,10 @@
     <t>total</t>
   </si>
   <si>
-    <t>model1-first</t>
-  </si>
-  <si>
-    <t>model2-first</t>
+    <t>gpt-4o-mini-first</t>
+  </si>
+  <si>
+    <t>meta-llama/Llama-2-7b-chat-hf-first</t>
   </si>
 </sst>
 </file>

--- a/data/analysis_results/gpt-4.1_vs_Llama-2-7b-chat-hf/Mistral-7B-Instruct-v0.2/basic/total_votes_file.xlsx
+++ b/data/analysis_results/gpt-4.1_vs_Llama-2-7b-chat-hf/Mistral-7B-Instruct-v0.2/basic/total_votes_file.xlsx
@@ -37,10 +37,10 @@
     <t>total</t>
   </si>
   <si>
-    <t>gpt-4o-mini-first</t>
-  </si>
-  <si>
-    <t>meta-llama/Llama-2-7b-chat-hf-first</t>
+    <t>model1-first</t>
+  </si>
+  <si>
+    <t>model2-first</t>
   </si>
 </sst>
 </file>
